--- a/upload_performance_result/sglang_benchmark_2026-07-29.xlsx
+++ b/upload_performance_result/sglang_benchmark_2026-07-29.xlsx
@@ -1106,7 +1106,7 @@
         <v>nightly</v>
       </c>
       <c r="E9" t="str">
-        <v>FAILED</v>
+        <v>PASS</v>
       </c>
       <c r="F9" t="str">
         <v>TPOT≤50, 吞吐≥2031.71</v>
@@ -1136,43 +1136,43 @@
         <v>122</v>
       </c>
       <c r="O9" t="str">
-        <v>108.12</v>
+        <v>106.46</v>
       </c>
       <c r="P9" t="str">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="Q9" t="str">
-        <v>20931.57</v>
+        <v>17324.20</v>
       </c>
       <c r="R9" t="str">
-        <v>34698.96</v>
+        <v>26765.37</v>
       </c>
       <c r="S9" t="str">
-        <v>40.97</v>
+        <v>38.76</v>
       </c>
       <c r="T9" t="str">
-        <v>50.37</v>
+        <v>46.96</v>
       </c>
       <c r="U9" t="str">
-        <v>82343.19</v>
+        <v>75424.33</v>
       </c>
       <c r="V9" t="str">
-        <v>1969.65</v>
+        <v>2117.18</v>
       </c>
       <c r="W9" t="str">
-        <v>1969.65</v>
+        <v>2117.18</v>
       </c>
       <c r="X9" t="str">
-        <v>6565.49</v>
+        <v>7057.28</v>
       </c>
       <c r="Y9" t="str">
-        <v>6565.49</v>
+        <v>7057.28</v>
       </c>
       <c r="Z9" t="str">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AA9" t="str">
-        <v>78.60</v>
+        <v>84.60</v>
       </c>
     </row>
     <row r="10">
@@ -1376,7 +1376,7 @@
         <v>gpqa</v>
       </c>
       <c r="L12">
-        <v>0.5455</v>
+        <v>0.5808</v>
       </c>
       <c r="M12">
         <v>256</v>
@@ -1385,43 +1385,43 @@
         <v>64</v>
       </c>
       <c r="O12" t="str">
-        <v>58.63</v>
+        <v>58.48</v>
       </c>
       <c r="P12" t="str">
-        <v>1.20</v>
+        <v>1.22</v>
       </c>
       <c r="Q12" t="str">
-        <v>4463.09</v>
+        <v>4409.10</v>
       </c>
       <c r="R12" t="str">
-        <v>10087.42</v>
+        <v>10080.01</v>
       </c>
       <c r="S12" t="str">
-        <v>29.63</v>
+        <v>28.99</v>
       </c>
       <c r="T12" t="str">
-        <v>40.47</v>
+        <v>39.19</v>
       </c>
       <c r="U12" t="str">
-        <v>48881.91</v>
+        <v>47869.74</v>
       </c>
       <c r="V12" t="str">
-        <v>1798.99</v>
+        <v>1832.60</v>
       </c>
       <c r="W12" t="str">
-        <v>1798.99</v>
+        <v>1832.60</v>
       </c>
       <c r="X12" t="str">
-        <v>5996.62</v>
+        <v>6108.67</v>
       </c>
       <c r="Y12" t="str">
-        <v>5996.62</v>
+        <v>6108.67</v>
       </c>
       <c r="Z12" t="str">
-        <v>1.20</v>
+        <v>1.22</v>
       </c>
       <c r="AA12" t="str">
-        <v>72.00</v>
+        <v>73.20</v>
       </c>
     </row>
     <row r="13">
@@ -1468,43 +1468,43 @@
         <v>16</v>
       </c>
       <c r="O13" t="str">
-        <v>15.76</v>
+        <v>15.79</v>
       </c>
       <c r="P13" t="str">
-        <v>0.80</v>
+        <v>0.71</v>
       </c>
       <c r="Q13" t="str">
-        <v>4810.25</v>
+        <v>4839.35</v>
       </c>
       <c r="R13" t="str">
-        <v>4928.62</v>
+        <v>4957.33</v>
       </c>
       <c r="S13" t="str">
-        <v>9.87</v>
+        <v>11.52</v>
       </c>
       <c r="T13" t="str">
-        <v>9.97</v>
+        <v>11.60</v>
       </c>
       <c r="U13" t="str">
-        <v>19606.53</v>
+        <v>22114.30</v>
       </c>
       <c r="V13" t="str">
-        <v>1205.68</v>
+        <v>1071.34</v>
       </c>
       <c r="W13" t="str">
-        <v>602.84</v>
+        <v>535.67</v>
       </c>
       <c r="X13" t="str">
-        <v>6144.16</v>
+        <v>5459.57</v>
       </c>
       <c r="Y13" t="str">
-        <v>3072.08</v>
+        <v>2729.78</v>
       </c>
       <c r="Z13" t="str">
-        <v>0.80</v>
+        <v>0.71</v>
       </c>
       <c r="AA13" t="str">
-        <v>48.00</v>
+        <v>42.60</v>
       </c>
     </row>
     <row r="14">
@@ -2215,43 +2215,43 @@
         <v>160</v>
       </c>
       <c r="O22" t="str">
-        <v>136.91</v>
+        <v>141.28</v>
       </c>
       <c r="P22" t="str">
-        <v>2.39</v>
+        <v>2.46</v>
       </c>
       <c r="Q22" t="str">
-        <v>4061.32</v>
+        <v>4136.80</v>
       </c>
       <c r="R22" t="str">
-        <v>11786.68</v>
+        <v>11792.18</v>
       </c>
       <c r="S22" t="str">
-        <v>35.49</v>
+        <v>35.56</v>
       </c>
       <c r="T22" t="str">
-        <v>50.28</v>
+        <v>51.05</v>
       </c>
       <c r="U22" t="str">
-        <v>57266.13</v>
+        <v>57446.95</v>
       </c>
       <c r="V22" t="str">
-        <v>3586.03</v>
+        <v>3689.04</v>
       </c>
       <c r="W22" t="str">
-        <v>3586.03</v>
+        <v>3689.04</v>
       </c>
       <c r="X22" t="str">
-        <v>11953.43</v>
+        <v>12296.80</v>
       </c>
       <c r="Y22" t="str">
-        <v>11953.43</v>
+        <v>12296.80</v>
       </c>
       <c r="Z22" t="str">
-        <v>2.39</v>
+        <v>2.46</v>
       </c>
       <c r="AA22" t="str">
-        <v>143.40</v>
+        <v>147.60</v>
       </c>
     </row>
     <row r="23">
@@ -2304,31 +2304,31 @@
         <v>0.05</v>
       </c>
       <c r="Q23" t="str">
-        <v>892.23</v>
+        <v>889.78</v>
       </c>
       <c r="R23" t="str">
-        <v>892.23</v>
+        <v>889.78</v>
       </c>
       <c r="S23" t="str">
-        <v>5.12</v>
+        <v>5.19</v>
       </c>
       <c r="T23" t="str">
-        <v>5.12</v>
+        <v>5.19</v>
       </c>
       <c r="U23" t="str">
-        <v>21384.14</v>
+        <v>21657.96</v>
       </c>
       <c r="V23" t="str">
-        <v>186.93</v>
+        <v>184.57</v>
       </c>
       <c r="W23" t="str">
-        <v>23.37</v>
+        <v>23.07</v>
       </c>
       <c r="X23" t="str">
-        <v>1028.13</v>
+        <v>1015.13</v>
       </c>
       <c r="Y23" t="str">
-        <v>128.52</v>
+        <v>126.89</v>
       </c>
       <c r="Z23" t="str">
         <v>0.05</v>
@@ -2381,43 +2381,43 @@
         <v>100</v>
       </c>
       <c r="O24" t="str">
-        <v>92.05</v>
+        <v>90.18</v>
       </c>
       <c r="P24" t="str">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Q24" t="str">
-        <v>7441.31</v>
+        <v>7429.07</v>
       </c>
       <c r="R24" t="str">
-        <v>18036.60</v>
+        <v>18053.70</v>
       </c>
       <c r="S24" t="str">
-        <v>44.88</v>
+        <v>45.11</v>
       </c>
       <c r="T24" t="str">
-        <v>63.46</v>
+        <v>63.29</v>
       </c>
       <c r="U24" t="str">
-        <v>76337.24</v>
+        <v>76679.53</v>
       </c>
       <c r="V24" t="str">
-        <v>1852.23</v>
+        <v>1806.52</v>
       </c>
       <c r="W24" t="str">
-        <v>926.12</v>
+        <v>903.26</v>
       </c>
       <c r="X24" t="str">
-        <v>6174.11</v>
+        <v>6021.73</v>
       </c>
       <c r="Y24" t="str">
-        <v>3087.05</v>
+        <v>3010.86</v>
       </c>
       <c r="Z24" t="str">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AA24" t="str">
-        <v>72.60</v>
+        <v>70.80</v>
       </c>
     </row>
     <row r="25">
@@ -2796,43 +2796,43 @@
         <v>16</v>
       </c>
       <c r="O29" t="str">
-        <v>12.65</v>
+        <v>12.69</v>
       </c>
       <c r="P29" t="str">
-        <v>0.80</v>
+        <v>0.81</v>
       </c>
       <c r="Q29" t="str">
-        <v>2772.28</v>
+        <v>2759.67</v>
       </c>
       <c r="R29" t="str">
-        <v>3767.82</v>
+        <v>3750.68</v>
       </c>
       <c r="S29" t="str">
-        <v>8.68</v>
+        <v>8.66</v>
       </c>
       <c r="T29" t="str">
-        <v>10.83</v>
+        <v>10.76</v>
       </c>
       <c r="U29" t="str">
-        <v>15782.01</v>
+        <v>15741.37</v>
       </c>
       <c r="V29" t="str">
-        <v>1202.00</v>
+        <v>1209.26</v>
       </c>
       <c r="W29" t="str">
-        <v>1202.00</v>
+        <v>1209.26</v>
       </c>
       <c r="X29" t="str">
-        <v>6125.41</v>
+        <v>6162.40</v>
       </c>
       <c r="Y29" t="str">
-        <v>6125.41</v>
+        <v>6162.40</v>
       </c>
       <c r="Z29" t="str">
-        <v>0.80</v>
+        <v>0.81</v>
       </c>
       <c r="AA29" t="str">
-        <v>48.00</v>
+        <v>48.60</v>
       </c>
     </row>
     <row r="30">
@@ -2926,7 +2926,7 @@
         <v>test_npu_mimo_v2_flash_1p1d_12p_in16k_out1_ttft_5s</v>
       </c>
       <c r="C31" t="str">
-        <v>20260728</v>
+        <v>20260729</v>
       </c>
       <c r="D31" t="str">
         <v>nightly</v>
@@ -2962,16 +2962,16 @@
         <v>64</v>
       </c>
       <c r="O31" t="str">
-        <v>0.50</v>
+        <v>0.53</v>
       </c>
       <c r="P31" t="str">
         <v>0.40</v>
       </c>
       <c r="Q31" t="str">
-        <v>1243.68</v>
+        <v>1331.81</v>
       </c>
       <c r="R31" t="str">
-        <v>2558.65</v>
+        <v>3136.77</v>
       </c>
       <c r="S31" t="str">
         <v>0.00</v>
@@ -2980,7 +2980,7 @@
         <v>0.00</v>
       </c>
       <c r="U31" t="str">
-        <v>1250.05</v>
+        <v>1338.11</v>
       </c>
       <c r="V31" t="str">
         <v>0.40</v>
@@ -2989,10 +2989,10 @@
         <v>0.03</v>
       </c>
       <c r="X31" t="str">
-        <v>6369.53</v>
+        <v>6369.42</v>
       </c>
       <c r="Y31" t="str">
-        <v>530.79</v>
+        <v>530.78</v>
       </c>
       <c r="Z31" t="str">
         <v>0.40</v>
@@ -3673,7 +3673,7 @@
         <v>deepseek_r1_w4a8_1p1d_16p_in3k5_out1k5_50ms</v>
       </c>
       <c r="C40" t="str">
-        <v>20260728</v>
+        <v>20260729</v>
       </c>
       <c r="D40" t="str">
         <v>fulltest</v>
@@ -3709,43 +3709,43 @@
         <v>416</v>
       </c>
       <c r="O40" t="str">
-        <v>363.13</v>
+        <v>364.23</v>
       </c>
       <c r="P40" t="str">
-        <v>4.31</v>
+        <v>4.38</v>
       </c>
       <c r="Q40" t="str">
-        <v>19606.01</v>
+        <v>18222.28</v>
       </c>
       <c r="R40" t="str">
-        <v>42049.59</v>
+        <v>38359.67</v>
       </c>
       <c r="S40" t="str">
-        <v>42.10</v>
+        <v>42.35</v>
       </c>
       <c r="T40" t="str">
-        <v>47.63</v>
+        <v>47.84</v>
       </c>
       <c r="U40" t="str">
-        <v>84222.55</v>
+        <v>83234.15</v>
       </c>
       <c r="V40" t="str">
-        <v>6622.63</v>
+        <v>6721.49</v>
       </c>
       <c r="W40" t="str">
-        <v>413.91</v>
+        <v>420.09</v>
       </c>
       <c r="X40" t="str">
-        <v>22075.45</v>
+        <v>22404.96</v>
       </c>
       <c r="Y40" t="str">
-        <v>1379.72</v>
+        <v>1400.31</v>
       </c>
       <c r="Z40" t="str">
-        <v>4.31</v>
+        <v>4.38</v>
       </c>
       <c r="AA40" t="str">
-        <v>258.60</v>
+        <v>262.80</v>
       </c>
     </row>
     <row r="41">
@@ -5914,7 +5914,7 @@
         <v>test_npu_mimo_v2_flash_1p1d_12p_in16k_out1k_tpot_20ms</v>
       </c>
       <c r="C67" t="str">
-        <v>20260728</v>
+        <v>20260729</v>
       </c>
       <c r="D67" t="str">
         <v>nightly</v>
@@ -5950,43 +5950,43 @@
         <v>32</v>
       </c>
       <c r="O67" t="str">
-        <v>24.49</v>
+        <v>28.13</v>
       </c>
       <c r="P67" t="str">
-        <v>1.04</v>
+        <v>1.33</v>
       </c>
       <c r="Q67" t="str">
-        <v>4579.90</v>
+        <v>4578.70</v>
       </c>
       <c r="R67" t="str">
-        <v>12305.63</v>
+        <v>12209.53</v>
       </c>
       <c r="S67" t="str">
-        <v>19.02</v>
+        <v>16.63</v>
       </c>
       <c r="T67" t="str">
-        <v>24.77</v>
+        <v>21.76</v>
       </c>
       <c r="U67" t="str">
-        <v>23576.76</v>
+        <v>21189.03</v>
       </c>
       <c r="V67" t="str">
-        <v>1038.74</v>
+        <v>1327.48</v>
       </c>
       <c r="W67" t="str">
-        <v>86.56</v>
+        <v>110.62</v>
       </c>
       <c r="X67" t="str">
-        <v>17658.61</v>
+        <v>22567.10</v>
       </c>
       <c r="Y67" t="str">
-        <v>1471.55</v>
+        <v>1880.59</v>
       </c>
       <c r="Z67" t="str">
-        <v>1.04</v>
+        <v>1.33</v>
       </c>
       <c r="AA67" t="str">
-        <v>62.40</v>
+        <v>79.80</v>
       </c>
     </row>
     <row r="68">
@@ -6439,7 +6439,7 @@
         <v>gpqa</v>
       </c>
       <c r="L73">
-        <v>0.5707</v>
+        <v>0.596</v>
       </c>
       <c r="M73" t="str">
         <v/>
